--- a/Outputs/Scenarios/PtX_demand_IT_Hydrogen.xlsx
+++ b/Outputs/Scenarios/PtX_demand_IT_Hydrogen.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.004194814982415169</v>
       </c>
       <c r="K16" t="n">
-        <v>0.02784445856088109</v>
+        <v>0.0169556770774016</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.009281486186960364</v>
+        <v>0.02061622770018015</v>
       </c>
     </row>
     <row r="18">
@@ -1481,7 +1481,7 @@
         <v>6.044018326571965e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.009281486186960364</v>
+        <v>0.008835526157220065</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.006209912877846326</v>
       </c>
       <c r="K30" t="n">
-        <v>0.1490408412151787</v>
+        <v>0.09075731781472617</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.04968028040505958</v>
+        <v>0.1103508589474002</v>
       </c>
     </row>
     <row r="32">
@@ -1999,7 +1999,7 @@
         <v>0.0003268375198866488</v>
       </c>
       <c r="K42" t="n">
-        <v>0.04968028040505958</v>
+        <v>0.04729322526317152</v>
       </c>
     </row>
     <row r="43">
